--- a/Dados de Entrada/dados_experimentais_codigo.xlsx
+++ b/Dados de Entrada/dados_experimentais_codigo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\Dropbox\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\OneDrive\Documentos\Vitor\Projetos\PycharmProjects\Projeto_TotalEnergies\Dados de Entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD7CD60-BD79-4603-9B86-0FFD0346FB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE8D62B-B3F9-46E0-BE20-1A230712A39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="785" activeTab="1" xr2:uid="{0506B892-8FEF-410F-A807-A4815D37E0A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="785" firstSheet="47" activeTab="1" xr2:uid="{0506B892-8FEF-410F-A807-A4815D37E0A7}"/>
   </bookViews>
   <sheets>
     <sheet name="MODELO" sheetId="18" r:id="rId1"/>
@@ -28,68 +28,69 @@
     <sheet name="Alves_BR3_25C" sheetId="11" r:id="rId13"/>
     <sheet name="Alves_BR3_50C" sheetId="12" r:id="rId14"/>
     <sheet name="Rolim_A_hept" sheetId="13" r:id="rId15"/>
-    <sheet name="Tharanivasan_L_hept" sheetId="14" r:id="rId16"/>
-    <sheet name="Tharanivasan_L_heptM" sheetId="17" r:id="rId17"/>
-    <sheet name="Tharanivasan_L_pent" sheetId="15" r:id="rId18"/>
-    <sheet name="Akbarzadeh_A_hept" sheetId="19" r:id="rId19"/>
-    <sheet name="Akbarzadeh_A_pent" sheetId="20" r:id="rId20"/>
-    <sheet name="Akbarzadeh_CL_hept" sheetId="21" r:id="rId21"/>
-    <sheet name="Akbarzadeh_CL_pent" sheetId="22" r:id="rId22"/>
-    <sheet name="Akbarzadeh_L_hept" sheetId="23" r:id="rId23"/>
-    <sheet name="Akbarzadeh_L_pent" sheetId="24" r:id="rId24"/>
-    <sheet name="Akbarzadeh_V1_hept" sheetId="25" r:id="rId25"/>
-    <sheet name="Akbarzadeh_V1_pent" sheetId="26" r:id="rId26"/>
-    <sheet name="Akbarzadeh_V2_hept" sheetId="27" r:id="rId27"/>
-    <sheet name="Akbarzadeh_V2_pent" sheetId="28" r:id="rId28"/>
-    <sheet name="Akbarzadeh_R_hept" sheetId="29" r:id="rId29"/>
-    <sheet name="Akbarzadeh_R_pent" sheetId="30" r:id="rId30"/>
-    <sheet name="Akbarzadeh_I_pent" sheetId="31" r:id="rId31"/>
-    <sheet name="Powers_VB-B2" sheetId="32" r:id="rId32"/>
-    <sheet name="Powers_VB-TC17" sheetId="33" r:id="rId33"/>
-    <sheet name="Powers_VB-TC51" sheetId="34" r:id="rId34"/>
-    <sheet name="Powers_B-C1" sheetId="35" r:id="rId35"/>
-    <sheet name="Powers_DB-A2" sheetId="36" r:id="rId36"/>
-    <sheet name="Powers_CO-A1" sheetId="37" r:id="rId37"/>
-    <sheet name="Powers_B-IS10" sheetId="38" r:id="rId38"/>
-    <sheet name="Powers_B-IS3" sheetId="39" r:id="rId39"/>
-    <sheet name="Powers_B-IS2" sheetId="40" r:id="rId40"/>
-    <sheet name="Powers_SR-A3" sheetId="41" r:id="rId41"/>
-    <sheet name="Powers_SR-HC70" sheetId="42" r:id="rId42"/>
-    <sheet name="Powers_SR-HC80" sheetId="43" r:id="rId43"/>
-    <sheet name="Tharanivasan_GoM" sheetId="44" r:id="rId44"/>
-    <sheet name="Johnston_B-B3_21C" sheetId="45" r:id="rId45"/>
-    <sheet name="Johnston_B-B3_23C" sheetId="46" r:id="rId46"/>
-    <sheet name="Johnston_B-B3_90C_4.8" sheetId="47" r:id="rId47"/>
-    <sheet name="Johnston_B-B3_140C_4.8" sheetId="48" r:id="rId48"/>
-    <sheet name="Johnston_B-B3_180C_4.8" sheetId="49" r:id="rId49"/>
-    <sheet name="Johnston_B-B3_180C_13.8" sheetId="50" r:id="rId50"/>
-    <sheet name="Johnston_B-B3_250C_10.3" sheetId="51" r:id="rId51"/>
-    <sheet name="Alboudwarej_L_pent" sheetId="52" r:id="rId52"/>
-    <sheet name="Alboudwarej_L_hex" sheetId="54" r:id="rId53"/>
-    <sheet name="Alboudwarej_L_hept" sheetId="55" r:id="rId54"/>
-    <sheet name="Alboudwarej_L_oct" sheetId="53" r:id="rId55"/>
-    <sheet name="Alboudwarej_A_pent" sheetId="56" r:id="rId56"/>
-    <sheet name="Alboudwarej_A_hex" sheetId="59" r:id="rId57"/>
-    <sheet name="Alboudwarej_A_hept" sheetId="58" r:id="rId58"/>
-    <sheet name="Alboudwarej_CL_pent" sheetId="60" r:id="rId59"/>
-    <sheet name="Alboudwarej_CL_hex" sheetId="62" r:id="rId60"/>
-    <sheet name="Alboudwarej_CL_hept" sheetId="61" r:id="rId61"/>
-    <sheet name="Rivero-Sanchez_B-A3_cond1" sheetId="63" r:id="rId62"/>
-    <sheet name="Rivero-Sanchez_B-A3_cond2" sheetId="66" r:id="rId63"/>
-    <sheet name="Rivero-Sanchez_B-A3_hept" sheetId="65" r:id="rId64"/>
-    <sheet name="Rivero-Sanchez_B-A3_D1" sheetId="67" r:id="rId65"/>
-    <sheet name="Rivero-Sanchez_B-A3_85C7+15D1" sheetId="64" r:id="rId66"/>
-    <sheet name="Rivero-Sanchez_B-A3_70C7+30D1" sheetId="68" r:id="rId67"/>
-    <sheet name="Rivero-Sanchez_B-A3_D3" sheetId="69" r:id="rId68"/>
-    <sheet name="Rivero-Sanchez_B-A3_85C7+15D3" sheetId="70" r:id="rId69"/>
-    <sheet name="Rivero-Sanchez_B-A3_70C7+30D3" sheetId="71" r:id="rId70"/>
-    <sheet name="Rivero-Sanchez_B-A3_KER" sheetId="72" r:id="rId71"/>
-    <sheet name="Rivero-Sanchez_B-A3_85C7+15KER" sheetId="73" r:id="rId72"/>
-    <sheet name="Rivero-Sanchez_B-A3_70C7+30KER" sheetId="74" r:id="rId73"/>
-    <sheet name="Rivero-Sanchez_B-A3_NAPH" sheetId="75" r:id="rId74"/>
+    <sheet name="Rolim_A_dec" sheetId="77" r:id="rId16"/>
+    <sheet name="Tharanivasan_L_hept" sheetId="14" r:id="rId17"/>
+    <sheet name="Tharanivasan_L_heptM" sheetId="17" r:id="rId18"/>
+    <sheet name="Tharanivasan_L_pent" sheetId="15" r:id="rId19"/>
+    <sheet name="Akbarzadeh_A_hept" sheetId="19" r:id="rId20"/>
+    <sheet name="Akbarzadeh_A_pent" sheetId="20" r:id="rId21"/>
+    <sheet name="Akbarzadeh_CL_hept" sheetId="21" r:id="rId22"/>
+    <sheet name="Akbarzadeh_CL_pent" sheetId="22" r:id="rId23"/>
+    <sheet name="Akbarzadeh_L_hept" sheetId="23" r:id="rId24"/>
+    <sheet name="Akbarzadeh_L_pent" sheetId="24" r:id="rId25"/>
+    <sheet name="Akbarzadeh_V1_hept" sheetId="25" r:id="rId26"/>
+    <sheet name="Akbarzadeh_V1_pent" sheetId="26" r:id="rId27"/>
+    <sheet name="Akbarzadeh_V2_hept" sheetId="27" r:id="rId28"/>
+    <sheet name="Akbarzadeh_V2_pent" sheetId="28" r:id="rId29"/>
+    <sheet name="Akbarzadeh_R_hept" sheetId="29" r:id="rId30"/>
+    <sheet name="Akbarzadeh_R_pent" sheetId="30" r:id="rId31"/>
+    <sheet name="Akbarzadeh_I_pent" sheetId="31" r:id="rId32"/>
+    <sheet name="Powers_VB-B2" sheetId="32" r:id="rId33"/>
+    <sheet name="Powers_VB-TC17" sheetId="33" r:id="rId34"/>
+    <sheet name="Powers_VB-TC51" sheetId="34" r:id="rId35"/>
+    <sheet name="Powers_B-C1" sheetId="35" r:id="rId36"/>
+    <sheet name="Powers_DB-A2" sheetId="36" r:id="rId37"/>
+    <sheet name="Powers_CO-A1" sheetId="37" r:id="rId38"/>
+    <sheet name="Powers_B-IS10" sheetId="38" r:id="rId39"/>
+    <sheet name="Powers_B-IS3" sheetId="39" r:id="rId40"/>
+    <sheet name="Powers_B-IS2" sheetId="40" r:id="rId41"/>
+    <sheet name="Powers_SR-A3" sheetId="41" r:id="rId42"/>
+    <sheet name="Powers_SR-HC70" sheetId="42" r:id="rId43"/>
+    <sheet name="Powers_SR-HC80" sheetId="43" r:id="rId44"/>
+    <sheet name="Tharanivasan_GoM" sheetId="44" r:id="rId45"/>
+    <sheet name="Johnston_B-B3_21C" sheetId="45" r:id="rId46"/>
+    <sheet name="Johnston_B-B3_23C" sheetId="46" r:id="rId47"/>
+    <sheet name="Johnston_B-B3_90C_4.8" sheetId="47" r:id="rId48"/>
+    <sheet name="Johnston_B-B3_140C_4.8" sheetId="48" r:id="rId49"/>
+    <sheet name="Johnston_B-B3_180C_4.8" sheetId="49" r:id="rId50"/>
+    <sheet name="Johnston_B-B3_180C_13.8" sheetId="50" r:id="rId51"/>
+    <sheet name="Johnston_B-B3_250C_10.3" sheetId="51" r:id="rId52"/>
+    <sheet name="Alboudwarej_L_pent" sheetId="52" r:id="rId53"/>
+    <sheet name="Alboudwarej_L_hex" sheetId="54" r:id="rId54"/>
+    <sheet name="Alboudwarej_L_hept" sheetId="55" r:id="rId55"/>
+    <sheet name="Alboudwarej_L_oct" sheetId="53" r:id="rId56"/>
+    <sheet name="Alboudwarej_A_pent" sheetId="56" r:id="rId57"/>
+    <sheet name="Alboudwarej_A_hex" sheetId="59" r:id="rId58"/>
+    <sheet name="Alboudwarej_A_hept" sheetId="58" r:id="rId59"/>
+    <sheet name="Alboudwarej_CL_pent" sheetId="60" r:id="rId60"/>
+    <sheet name="Alboudwarej_CL_hex" sheetId="62" r:id="rId61"/>
+    <sheet name="Alboudwarej_CL_hept" sheetId="61" r:id="rId62"/>
+    <sheet name="Rivero-Sanchez_B-A3_cond1" sheetId="63" r:id="rId63"/>
+    <sheet name="Rivero-Sanchez_B-A3_cond2" sheetId="66" r:id="rId64"/>
+    <sheet name="Rivero-Sanchez_B-A3_hept" sheetId="65" r:id="rId65"/>
+    <sheet name="Rivero-Sanchez_B-A3_D1" sheetId="67" r:id="rId66"/>
+    <sheet name="Rivero-Sanchez_B-A3_85C7+15D1" sheetId="64" r:id="rId67"/>
+    <sheet name="Rivero-Sanchez_B-A3_70C7+30D1" sheetId="68" r:id="rId68"/>
+    <sheet name="Rivero-Sanchez_B-A3_D3" sheetId="69" r:id="rId69"/>
+    <sheet name="Rivero-Sanchez_B-A3_85C7+15D3" sheetId="70" r:id="rId70"/>
+    <sheet name="Rivero-Sanchez_B-A3_70C7+30D3" sheetId="71" r:id="rId71"/>
+    <sheet name="Rivero-Sanchez_B-A3_KER" sheetId="72" r:id="rId72"/>
+    <sheet name="Rivero-Sanchez_B-A3_85C7+15KER" sheetId="73" r:id="rId73"/>
+    <sheet name="Rivero-Sanchez_B-A3_70C7+30KER" sheetId="74" r:id="rId74"/>
+    <sheet name="Rivero-Sanchez_B-A3_NAPH" sheetId="75" r:id="rId75"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CONTROLE DE DADOS'!$A$1:$G$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CONTROLE DE DADOS'!$A$1:$G$74</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -112,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="212">
   <si>
     <t>Nome Planilha</t>
   </si>
@@ -265,9 +266,6 @@
   </si>
   <si>
     <t>Tabela da Tese Saidoun (2020).</t>
-  </si>
-  <si>
-    <t>Medidas do David.</t>
   </si>
   <si>
     <t>Tharanivasan_L_hept</t>
@@ -759,6 +757,21 @@
   </si>
   <si>
     <t>Mesmo óleo P3.</t>
+  </si>
+  <si>
+    <t>n-decano</t>
+  </si>
+  <si>
+    <t>Medidas do David, Leonarda e Mikael.</t>
+  </si>
+  <si>
+    <t>Rolim_A_dec</t>
+  </si>
+  <si>
+    <t>Tempos: 24h, 2h, 1h. Dados cinéticos ainda sob análise.</t>
+  </si>
+  <si>
+    <t>Tempos: 24h, 2h. Dados cinéticos ainda sob análise.</t>
   </si>
 </sst>
 </file>
@@ -792,7 +805,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -814,6 +827,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1038,6 +1057,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2729,6 +2754,9 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6CC954F-2674-4D40-9EC4-491AA1E7582E}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2763,7 +2791,9 @@
       <c r="F2" s="13">
         <v>2</v>
       </c>
-      <c r="G2" s="13"/>
+      <c r="G2" s="13">
+        <v>1</v>
+      </c>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
@@ -2808,9 +2838,12 @@
         <v>0.4</v>
       </c>
       <c r="E4" s="10">
-        <v>7.2972831099999969E-3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2830,6 +2863,9 @@
       <c r="F5" s="8">
         <v>0</v>
       </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -2842,9 +2878,12 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="9">
-        <v>3.3985556000000017E-3</v>
+        <v>3.3985555999999986E-3</v>
       </c>
       <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2864,6 +2903,9 @@
       <c r="F7" s="8">
         <v>0</v>
       </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
@@ -2876,9 +2918,12 @@
         <v>0.6</v>
       </c>
       <c r="E8" s="9">
-        <v>1.5312316120000001E-2</v>
+        <v>1.5312316119999995E-2</v>
       </c>
       <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2893,10 +2938,13 @@
         <v>0.65</v>
       </c>
       <c r="E9" s="9">
-        <v>2.7977816310000004E-2</v>
+        <v>2.797781631E-2</v>
       </c>
       <c r="F9" s="8">
-        <v>3.4414274799999946E-3</v>
+        <v>3.441427479999995E-3</v>
+      </c>
+      <c r="G9" s="8">
+        <v>5.7715619599999976E-3</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -2909,11 +2957,12 @@
       <c r="D10" s="8">
         <v>0.7</v>
       </c>
-      <c r="E10" s="8">
-        <v>1.5297170089999996E-2</v>
-      </c>
+      <c r="E10" s="8"/>
       <c r="F10" s="8">
-        <v>1.3719833929999998E-2</v>
+        <v>1.3719833929999994E-2</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1.6445294219999997E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -2926,6 +2975,9 @@
       <c r="F11" s="8">
         <v>1.6089932469999998E-2</v>
       </c>
+      <c r="G11" s="8">
+        <v>2.2706969309999991E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
@@ -2939,7 +2991,10 @@
         <v>4.6076683329999993E-2</v>
       </c>
       <c r="F12" s="8">
-        <v>2.033266609E-2</v>
+        <v>2.0332666089999993E-2</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2.0653098539999998E-2</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2955,6 +3010,9 @@
       </c>
       <c r="F13" s="8">
         <v>3.1975850550000004E-2</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2.6152530849999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2967,7 +3025,10 @@
         <v>6.454130939000001E-2</v>
       </c>
       <c r="F14" s="8">
-        <v>4.2157725070000006E-2</v>
+        <v>4.2157725069999999E-2</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4.2244506639999985E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2984,7 +3045,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>51</v>
+        <v>208</v>
       </c>
       <c r="B17" s="31"/>
       <c r="D17" s="8"/>
@@ -3012,6 +3073,293 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBD26CF-9DDC-4E42-B222-DC90027411C9}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="17.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13">
+        <v>2</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5">
+        <v>42.8</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <v>11.1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.6167099999999997E-2</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.6</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2.3841099999999997E-2</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1.27805E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3.6436400000000001E-2</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2.0493700000000004E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="E10" s="8">
+        <v>4.6747700000000003E-2</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2.63959E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E11" s="8">
+        <v>5.1457200000000008E-2</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2.86533E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="D12" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5.4457500000000006E-2</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2.8008499999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="D13" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="E13" s="8">
+        <v>4.9335599999999993E-2</v>
+      </c>
+      <c r="F13" s="8">
+        <v>3.1226799999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="D14" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="8">
+        <v>5.92916E-2</v>
+      </c>
+      <c r="F14" s="8">
+        <v>3.8832000000000005E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{739B5203-D1AE-41EE-B576-C19A27B42CEF}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3029,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3037,7 +3385,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -3056,7 +3404,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>7</v>
@@ -3209,7 +3557,7 @@
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -3241,7 +3589,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="31"/>
       <c r="D17" s="8"/>
@@ -3268,7 +3616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFB98FD-DCA5-4C30-B911-F8174270C52B}">
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3286,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3294,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -3313,7 +3661,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>7</v>
@@ -3466,7 +3814,7 @@
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -3510,7 +3858,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="31"/>
       <c r="D17" s="8">
@@ -3685,7 +4033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A16E60-8044-47BF-9DBF-E09886368CBE}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3703,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3711,7 +4059,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -3730,7 +4078,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>7</v>
@@ -3849,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.71327429398065101</v>
@@ -3883,7 +4231,7 @@
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -3919,7 +4267,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="31"/>
       <c r="D17" s="8"/>
@@ -3934,239 +4282,6 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E52E4E-A103-4DB8-9368-B533F95F2C87}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="24">
-        <v>0.577892573631961</v>
-      </c>
-      <c r="E4" s="24">
-        <v>3.2804299044826499E-3</v>
-      </c>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>16.3</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.70557853507543244</v>
-      </c>
-      <c r="E5" s="24">
-        <v>3.1746033072381399E-2</v>
-      </c>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.70619838870966345</v>
-      </c>
-      <c r="E6" s="24">
-        <v>3.6296300521392703E-2</v>
-      </c>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>28.5</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.77376033518098475</v>
-      </c>
-      <c r="E7" s="8">
-        <v>4.43386263646715E-2</v>
-      </c>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>14.7</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.77376033518098475</v>
-      </c>
-      <c r="E8" s="8">
-        <v>4.6349206614476203E-2</v>
-      </c>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.84566120034435877</v>
-      </c>
-      <c r="E9" s="8">
-        <v>5.4391537301814598E-2</v>
-      </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.89214880422259124</v>
-      </c>
-      <c r="E10" s="8">
-        <v>5.8624339612372997E-2</v>
-      </c>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D11" s="8">
-        <v>0.9330578956354354</v>
-      </c>
-      <c r="E11" s="8">
-        <v>6.4126985522534596E-2</v>
-      </c>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="D12" s="8">
-        <v>0.95537194549698645</v>
-      </c>
-      <c r="E12" s="8">
-        <v>6.6455028488762599E-2</v>
-      </c>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4184,7 +4299,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultColWidth="27.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" style="1" customWidth="1"/>
@@ -4204,19 +4319,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4227,7 +4342,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>23</v>
@@ -4239,7 +4354,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -4250,7 +4365,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>26</v>
@@ -4262,7 +4377,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -4273,7 +4388,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>29</v>
@@ -4285,7 +4400,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4296,7 +4411,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>33</v>
@@ -4308,7 +4423,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4319,7 +4434,7 @@
         <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>39</v>
@@ -4331,7 +4446,7 @@
         <v>17</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4342,7 +4457,7 @@
         <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>44</v>
@@ -4354,7 +4469,7 @@
         <v>17</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -4365,7 +4480,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>33</v>
@@ -4377,7 +4492,7 @@
         <v>17</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -4388,7 +4503,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>39</v>
@@ -4400,7 +4515,7 @@
         <v>17</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -4411,7 +4526,7 @@
         <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>44</v>
@@ -4423,7 +4538,7 @@
         <v>17</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -4434,7 +4549,7 @@
         <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>33</v>
@@ -4446,7 +4561,7 @@
         <v>17</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4457,7 +4572,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>39</v>
@@ -4469,7 +4584,7 @@
         <v>17</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -4480,7 +4595,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>44</v>
@@ -4492,384 +4607,390 @@
         <v>17</v>
       </c>
       <c r="G13" s="23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="32">
+        <v>25</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="32">
+        <v>25</v>
+      </c>
+      <c r="F15" s="32" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="1">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="1">
-        <v>23</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>197</v>
+      <c r="G15" s="33" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E16" s="1">
         <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>195</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1">
         <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="E19" s="1">
         <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="E20" s="1">
         <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" s="1">
         <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E22" s="1">
         <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1">
         <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="E24" s="1">
         <v>23</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="1">
         <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C26" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1">
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E27" s="1">
         <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="C28" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E28" s="1">
         <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E29" s="1">
         <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E30" s="1">
         <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E31" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E32" s="1">
         <v>20</v>
@@ -4880,16 +5001,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="E33" s="1">
         <v>20</v>
@@ -4900,16 +5021,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1">
         <v>20</v>
@@ -4920,16 +5041,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="E35" s="1">
         <v>20</v>
@@ -4939,60 +5060,60 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" s="1">
+        <v>20</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="28">
+      <c r="E37" s="28">
         <v>20</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F37" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="29" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="1">
-        <v>20</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>17</v>
+      <c r="G37" s="29" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E38" s="1">
         <v>20</v>
@@ -5003,16 +5124,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E39" s="1">
         <v>20</v>
@@ -5023,16 +5144,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E40" s="1">
         <v>20</v>
@@ -5043,16 +5164,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E41" s="1">
         <v>20</v>
@@ -5060,22 +5181,19 @@
       <c r="F41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="23" t="s">
-        <v>201</v>
-      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E42" s="1">
         <v>20</v>
@@ -5084,717 +5202,973 @@
         <v>17</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="E43" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="G43" s="23" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="E44" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="E45" s="1">
+        <v>21</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="1">
         <v>23</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="25">
-        <v>90</v>
-      </c>
-      <c r="F46" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>180</v>
+      <c r="F46" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B47" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>119</v>
-      </c>
       <c r="E47" s="25">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B48" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C48" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>119</v>
-      </c>
       <c r="E48" s="25">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G48" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B49" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" s="25" t="s">
         <v>118</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D49" s="25" t="s">
-        <v>119</v>
       </c>
       <c r="E49" s="25">
         <v>180</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G49" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B50" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D50" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>119</v>
-      </c>
       <c r="E50" s="25">
+        <v>180</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="25">
         <v>250</v>
       </c>
-      <c r="F50" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="28">
-        <v>50</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" s="29" t="s">
-        <v>199</v>
+      <c r="F51" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="28" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" s="28">
         <v>50</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="28">
         <v>50</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="G53" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E54" s="28">
         <v>50</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E55" s="28">
         <v>50</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56" s="28">
         <v>50</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57" s="28">
         <v>50</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="G57" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E58" s="28">
         <v>50</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G58" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E59" s="28">
         <v>50</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="G59" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E60" s="28">
         <v>50</v>
       </c>
       <c r="F60" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="28">
+        <v>50</v>
+      </c>
+      <c r="F61" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="29" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E61" s="25">
-        <v>21</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>192</v>
+      <c r="G61" s="29" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="25" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B62" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D62" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E62" s="25">
         <v>21</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B63" s="1" t="s">
+      <c r="A63" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="E63" s="25">
         <v>21</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E64" s="1">
+        <v>21</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E64" s="25">
-        <v>21</v>
-      </c>
-      <c r="F64" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B65" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D65" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C65" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E65" s="25">
         <v>21</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G65" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B66" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D66" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E66" s="25">
         <v>21</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B67" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C67" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D67" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E67" s="25">
         <v>21</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="25" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B68" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C68" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D68" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E68" s="25">
         <v>21</v>
       </c>
       <c r="F68" s="25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="25" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B69" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E69" s="25">
         <v>21</v>
       </c>
       <c r="F69" s="25" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="25" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B70" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D70" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E70" s="25">
         <v>21</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B71" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E71" s="25">
         <v>21</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B72" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D72" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E72" s="25">
         <v>21</v>
       </c>
       <c r="F72" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G72" s="26" t="s">
         <v>191</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B73" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D73" s="25" t="s">
         <v>147</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>148</v>
       </c>
       <c r="E73" s="25">
         <v>21</v>
       </c>
       <c r="F73" s="25" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E74" s="25">
+        <v>21</v>
+      </c>
+      <c r="F74" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G73" xr:uid="{853C675F-25A8-4644-AF1B-EB34412D5929}"/>
+  <autoFilter ref="A1:G74" xr:uid="{853C675F-25A8-4644-AF1B-EB34412D5929}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E52E4E-A103-4DB8-9368-B533F95F2C87}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0.577892573631961</v>
+      </c>
+      <c r="E4" s="24">
+        <v>3.2804299044826499E-3</v>
+      </c>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>16.3</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.70557853507543244</v>
+      </c>
+      <c r="E5" s="24">
+        <v>3.1746033072381399E-2</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.70619838870966345</v>
+      </c>
+      <c r="E6" s="24">
+        <v>3.6296300521392703E-2</v>
+      </c>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>28.5</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.77376033518098475</v>
+      </c>
+      <c r="E7" s="8">
+        <v>4.43386263646715E-2</v>
+      </c>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>14.7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.77376033518098475</v>
+      </c>
+      <c r="E8" s="8">
+        <v>4.6349206614476203E-2</v>
+      </c>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.84566120034435877</v>
+      </c>
+      <c r="E9" s="8">
+        <v>5.4391537301814598E-2</v>
+      </c>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.89214880422259124</v>
+      </c>
+      <c r="E10" s="8">
+        <v>5.8624339612372997E-2</v>
+      </c>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D11" s="8">
+        <v>0.9330578956354354</v>
+      </c>
+      <c r="E11" s="8">
+        <v>6.4126985522534596E-2</v>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="D12" s="8">
+        <v>0.95537194549698645</v>
+      </c>
+      <c r="E12" s="8">
+        <v>6.6455028488762599E-2</v>
+      </c>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="31"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2328CE99-A630-434B-AA6A-3F972801B5B5}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5812,7 +6186,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -5820,7 +6194,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -5839,7 +6213,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -5953,18 +6327,18 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="30"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -5980,7 +6354,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -5999,7 +6373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C678A8AE-CFDA-437A-9A54-6423B962D5A6}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6017,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -6025,7 +6399,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -6044,7 +6418,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -6197,7 +6571,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -6220,7 +6594,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -6239,7 +6613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D9447DC-BFEC-4718-BEC3-49D32E2C726F}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6257,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -6265,7 +6639,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -6284,7 +6658,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -6403,7 +6777,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.96049132484873445</v>
@@ -6421,7 +6795,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -6437,7 +6811,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -6456,7 +6830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68FAC68C-2C0C-40A2-A41D-40133AF7D86C}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6474,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -6482,7 +6856,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -6501,7 +6875,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -6654,7 +7028,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -6677,7 +7051,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -6696,7 +7070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE390DC7-9F32-44AB-B679-B83A98A90F90}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6714,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -6722,7 +7096,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -6741,7 +7115,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -6860,7 +7234,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.71406681264004179</v>
@@ -6894,7 +7268,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -6924,7 +7298,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -6943,7 +7317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7D3047-077E-48A3-B206-D42C45A966C1}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6961,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -6969,7 +7343,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -6988,7 +7362,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -7141,7 +7515,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -7171,7 +7545,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -7190,7 +7564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8606DE-E4DD-46BF-A1C4-52CF7C4BFD80}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7208,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -7216,7 +7590,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -7235,7 +7609,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -7354,7 +7728,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.92313498690182394</v>
@@ -7372,7 +7746,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -7388,7 +7762,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -7407,7 +7781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D277927F-850F-4B62-A649-637C566232F7}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7425,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -7433,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -7452,7 +7826,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -7598,7 +7972,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -7614,7 +7988,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -7633,7 +8007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75AB588-96B8-4F99-8EDF-4E044E970217}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7651,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -7659,7 +8033,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -7678,7 +8052,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -7797,7 +8171,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.92317824289657091</v>
@@ -7815,7 +8189,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -7831,254 +8205,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC8BA44-B704-4FEE-8F58-1CFBB33718CE}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.40496947106577685</v>
-      </c>
-      <c r="E4" s="8">
-        <v>4.2895657575547501E-4</v>
-      </c>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>25</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.40680034340787696</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1.5013403789321E-3</v>
-      </c>
-      <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>31.1</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.57646035475625146</v>
-      </c>
-      <c r="E6" s="8">
-        <v>6.0768555510563498E-3</v>
-      </c>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>37.1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.67227546411152717</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1.83020549613379E-2</v>
-      </c>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>6.8</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.73147338736782419</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.4307418386119301E-2</v>
-      </c>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.7723626523888748</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.9955317361420201E-2</v>
-      </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.77297298662674618</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.5317247831621497E-2</v>
-      </c>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D11" s="8">
-        <v>0.87183958791054694</v>
-      </c>
-      <c r="E11" s="8">
-        <v>4.2609473347457301E-2</v>
-      </c>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="D12" s="8">
-        <v>0.87306019120053269</v>
-      </c>
-      <c r="E12" s="8">
-        <v>4.3753351185961797E-2</v>
-      </c>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="31"/>
-      <c r="D13" s="8">
-        <v>0.93164778021895833</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.9678284715867998E-2</v>
-      </c>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="D14" s="8">
-        <v>0.93164778021895833</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4.5969616645749098E-2</v>
-      </c>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -8302,6 +8429,253 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC8BA44-B704-4FEE-8F58-1CFBB33718CE}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.40496947106577685</v>
+      </c>
+      <c r="E4" s="8">
+        <v>4.2895657575547501E-4</v>
+      </c>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>25</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.40680034340787696</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.5013403789321E-3</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>31.1</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.57646035475625146</v>
+      </c>
+      <c r="E6" s="8">
+        <v>6.0768555510563498E-3</v>
+      </c>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>37.1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.67227546411152717</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1.83020549613379E-2</v>
+      </c>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>6.8</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.73147338736782419</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.4307418386119301E-2</v>
+      </c>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.7723626523888748</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.9955317361420201E-2</v>
+      </c>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.77297298662674618</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.5317247831621497E-2</v>
+      </c>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D11" s="8">
+        <v>0.87183958791054694</v>
+      </c>
+      <c r="E11" s="8">
+        <v>4.2609473347457301E-2</v>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="D12" s="8">
+        <v>0.87306019120053269</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.3753351185961797E-2</v>
+      </c>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="D13" s="8">
+        <v>0.93164778021895833</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.9678284715867998E-2</v>
+      </c>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="D14" s="8">
+        <v>0.93164778021895833</v>
+      </c>
+      <c r="E14" s="8">
+        <v>4.5969616645749098E-2</v>
+      </c>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9A232D-43BF-4CBE-AC53-55E23074D704}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8319,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -8327,7 +8701,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -8346,7 +8720,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -8465,7 +8839,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.92493459249555032</v>
@@ -8483,7 +8857,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -8499,7 +8873,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -8518,7 +8892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21233698-8BE2-4DE4-89B1-A8120FA9BF5E}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8536,7 +8910,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -8544,7 +8918,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -8563,7 +8937,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -8676,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -8687,7 +9061,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -8703,7 +9077,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -8722,7 +9096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1677C279-E2CB-4654-A9BC-3B8CCF77B1F3}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8740,7 +9114,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -8748,7 +9122,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -8767,7 +9141,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -8885,7 +9259,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -8901,7 +9275,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -8920,7 +9294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10ACA54-F464-48D7-93E0-44C979C0EC49}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8938,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -8946,7 +9320,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -8965,7 +9339,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -9109,7 +9483,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -9125,7 +9499,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -9144,7 +9518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7150A8F9-99FD-42D5-BF10-0A8716B1E0FC}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9162,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -9170,7 +9544,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -9189,7 +9563,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -9333,7 +9707,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -9361,7 +9735,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -9380,7 +9754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77694E81-8D46-4CA3-9C5E-38E0031AF32A}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9398,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -9406,7 +9780,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -9425,7 +9799,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -9543,7 +9917,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -9559,7 +9933,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -9578,7 +9952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4473D956-CED2-4630-9933-3FFE808B0EB6}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9596,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -9604,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -9623,7 +9997,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -9767,7 +10141,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -9789,7 +10163,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -9808,7 +10182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8740A5DA-E1F5-4F03-954C-E9F36B0DD66F}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -9829,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -9837,7 +10211,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -9856,7 +10230,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -9978,7 +10352,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -9994,7 +10368,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -10013,7 +10387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004D3A67-1583-45A2-902A-E686D8AA24D9}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10031,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -10039,7 +10413,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -10058,7 +10432,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -10182,7 +10556,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -10198,225 +10572,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55637399-CFD4-45A0-9BB2-4B0BF84D3C54}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.43906810035842198</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1.0960975609756E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>21.4</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.44086021505376299</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1.8616260162601588E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>53.6</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.57347670250895999</v>
-      </c>
-      <c r="E6" s="8">
-        <v>4.819349593495928E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>14.3</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.648745519713261</v>
-      </c>
-      <c r="E7" s="8">
-        <v>6.6287804878048751E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>10.7</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.72759856630824304</v>
-      </c>
-      <c r="E8" s="8">
-        <v>8.4208130081300792E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>20</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.78315412186379896</v>
-      </c>
-      <c r="E9" s="8">
-        <v>8.8905691056910527E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.87992831541218597</v>
-      </c>
-      <c r="E10" s="8">
-        <v>9.8126829268292651E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>9.8126829268292651E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
         <v>86</v>
-      </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>87</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -10653,6 +10809,224 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55637399-CFD4-45A0-9BB2-4B0BF84D3C54}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.43906810035842198</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1.0960975609756E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>21.4</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.44086021505376299</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.8616260162601588E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.57347670250895999</v>
+      </c>
+      <c r="E6" s="8">
+        <v>4.819349593495928E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>14.3</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.648745519713261</v>
+      </c>
+      <c r="E7" s="8">
+        <v>6.6287804878048751E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>10.7</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.72759856630824304</v>
+      </c>
+      <c r="E8" s="8">
+        <v>8.4208130081300792E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.78315412186379896</v>
+      </c>
+      <c r="E9" s="8">
+        <v>8.8905691056910527E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.87992831541218597</v>
+      </c>
+      <c r="E10" s="8">
+        <v>9.8126829268292651E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>9.8126829268292651E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD5CC12-5BE7-4579-862E-69E7CB389A5F}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10670,7 +11044,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -10678,7 +11052,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -10697,7 +11071,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -10815,7 +11189,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -10831,7 +11205,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -10850,7 +11224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C806724-B004-4B95-B65B-2F70BE343FA5}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10868,7 +11242,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -10876,7 +11250,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -10895,7 +11269,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -11025,7 +11399,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -11041,7 +11415,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -11060,7 +11434,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F36758E-4019-4482-8822-8A7CD07EA4B4}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11078,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -11086,7 +11460,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -11105,7 +11479,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -11249,7 +11623,7 @@
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -11291,7 +11665,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" s="31"/>
       <c r="D17" s="8">
@@ -11316,7 +11690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA1579D-E08B-41FA-95F8-3F59305A1FFC}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11334,7 +11708,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -11342,7 +11716,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -11361,7 +11735,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -11514,7 +11888,7 @@
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -11560,7 +11934,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -11579,7 +11953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C13339-2031-4A25-98A0-A14B25E7477A}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11597,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -11605,7 +11979,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -11624,7 +11998,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -11777,7 +12151,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -11793,7 +12167,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -11812,7 +12186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C70D40-4EDB-47C1-866E-D31A67EB22BB}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11830,7 +12204,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -11838,7 +12212,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -11857,7 +12231,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -11970,7 +12344,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.71901279707495402</v>
@@ -12001,7 +12375,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -12029,7 +12403,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -12048,7 +12422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0B56F9-DABF-45C6-986B-83E2AAB41324}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12066,7 +12440,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -12074,7 +12448,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -12093,7 +12467,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -12206,7 +12580,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.71891891891891802</v>
@@ -12237,7 +12611,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -12265,7 +12639,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -12284,7 +12658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B032BD-9719-4092-9C83-EBA7E1DCFE63}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -12305,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -12313,7 +12687,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -12332,7 +12706,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -12445,7 +12819,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>0.78848263254113304</v>
@@ -12476,7 +12850,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -12492,7 +12866,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -12511,7 +12885,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C9CFE2-4173-40C6-911F-4C377D77E74A}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -12532,7 +12906,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -12540,7 +12914,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -12559,7 +12933,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -12666,7 +13040,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -12677,7 +13051,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -12693,234 +13067,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32E482B-7DD4-4D39-BD03-E3B5426D0F9C}">
-  <sheetPr>
-    <tabColor theme="2" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.50968921389396704</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.54351005484460702</v>
-      </c>
-      <c r="E5" s="8">
-        <v>8.5813148788927304E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>46.9</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.59287020109689204</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.124221453287197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>16.7</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.591956124314442</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.12802768166089901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.63765996343692799</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.135640138408304</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>180</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.64771480804387505</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.15259515570934201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.69524680073126099</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.16608996539792301</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D11" s="8">
-        <v>0.72541133455210205</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.173010380622837</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="D12" s="8">
-        <v>0.79853747714807999</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.183044982698961</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -13209,6 +13356,233 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F32E482B-7DD4-4D39-BD03-E3B5426D0F9C}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.50968921389396704</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.54351005484460702</v>
+      </c>
+      <c r="E5" s="8">
+        <v>8.5813148788927304E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46.9</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.59287020109689204</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.124221453287197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>16.7</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.591956124314442</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.12802768166089901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.63765996343692799</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.135640138408304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>180</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.64771480804387505</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.15259515570934201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.69524680073126099</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.16608996539792301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="8">
+        <v>0.72541133455210205</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.173010380622837</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="D12" s="8">
+        <v>0.79853747714807999</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.183044982698961</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA7C458-E807-45C9-83E7-33C94E656C19}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -13229,7 +13603,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -13237,7 +13611,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -13256,7 +13630,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -13351,7 +13725,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -13362,7 +13736,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -13378,7 +13752,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -13397,7 +13771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C8A921-DAF7-41A3-9218-55B041EC7C27}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -13418,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -13426,7 +13800,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -13445,7 +13819,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -13546,7 +13920,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -13557,7 +13931,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -13573,7 +13947,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -13592,7 +13966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C66DFF-9490-40F7-9685-22C48F391690}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -13613,7 +13987,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -13621,7 +13995,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -13640,7 +14014,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -13759,7 +14133,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8">
         <v>2.19108280254777E-2</v>
@@ -13793,7 +14167,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -13832,7 +14206,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -13851,7 +14225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFE8D06-C9C5-4C51-BF29-7050087C5F54}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -13872,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -13880,7 +14254,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -13899,7 +14273,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -14012,7 +14386,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D10" s="8">
         <v>6.5806451612903202E-2</v>
@@ -14037,7 +14411,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -14053,7 +14427,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -14072,7 +14446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC096F0A-8227-46A8-A8FA-920D2EF86799}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14093,7 +14467,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -14101,7 +14475,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -14120,7 +14494,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -14264,7 +14638,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -14286,7 +14660,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -14305,7 +14679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709DDC0C-8540-437C-A763-2D94AE6D0D6B}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14326,7 +14700,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -14334,7 +14708,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -14353,7 +14727,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -14466,7 +14840,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D10" s="8">
         <v>3.5031847133757898E-2</v>
@@ -14497,7 +14871,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -14513,7 +14887,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -14532,7 +14906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AAA5F1B-EBE2-47CF-AB0C-09D88C3E736A}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14553,7 +14927,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -14561,7 +14935,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -14580,7 +14954,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -14693,7 +15067,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -14704,7 +15078,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -14720,7 +15094,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -14739,7 +15113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C3AA5B-B3D5-45C3-A75D-5AF419A2735D}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14760,7 +15134,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -14768,7 +15142,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -14787,7 +15161,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -14900,7 +15274,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -14911,7 +15285,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -14927,7 +15301,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -14946,7 +15320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D785DE-1237-40AB-BD60-F0DBD75ADAB0}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -14967,7 +15341,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -14975,7 +15349,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -14994,7 +15368,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -15138,7 +15512,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -15154,184 +15528,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A62D91-F664-4AF7-8588-91F9652B0B69}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8">
-        <v>0.24901445466491401</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.156782608695652</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>38.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>26.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-    </row>
-    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
         <v>133</v>
-      </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>134</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -15588,6 +15785,183 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A62D91-F664-4AF7-8588-91F9652B0B69}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.24901445466491401</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.156782608695652</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+    </row>
+    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D91151C-EC68-422A-AEE4-0557F6C673DE}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15608,7 +15982,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -15616,7 +15990,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -15635,7 +16009,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -15748,7 +16122,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D10" s="8">
         <v>3.2522996057818603E-2</v>
@@ -15779,7 +16153,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -15801,7 +16175,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -15820,7 +16194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6A9DC7-61B1-472D-8D19-7F01A6F99C68}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -15841,7 +16215,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -15849,7 +16223,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -15868,7 +16242,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -16012,7 +16386,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -16028,7 +16402,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -16047,7 +16421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFDA971-D410-4BF8-AAF7-6449188B5304}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -16068,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -16076,7 +16450,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -16095,7 +16469,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -16208,7 +16582,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -16219,7 +16593,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -16235,7 +16609,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -16254,7 +16628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551CD329-812E-40DF-9704-B1CE60440007}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -16275,7 +16649,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -16283,7 +16657,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -16302,7 +16676,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -16415,7 +16789,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" s="8">
         <v>0.65</v>
@@ -16446,7 +16820,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
       <c r="D13" s="8">
@@ -16474,7 +16848,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -16493,7 +16867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71EE74FA-C35C-47F9-A286-0023C42E9E5F}">
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -16511,7 +16885,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -16519,7 +16893,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -16538,7 +16912,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -16668,7 +17042,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -16684,7 +17058,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -16703,7 +17077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B100361-EB55-418F-A0E5-492713E36F69}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -16724,7 +17098,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -16732,7 +17106,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -16751,7 +17125,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -16852,7 +17226,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -16863,7 +17237,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -16879,7 +17253,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -16898,7 +17272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5CAE53-DA80-464A-9300-3EB4849E79F1}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -16919,7 +17293,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -16927,7 +17301,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -16946,7 +17320,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -17059,7 +17433,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="8">
         <v>0.84955224051914202</v>
@@ -17084,7 +17458,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -17100,7 +17474,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -17119,7 +17493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D860AC99-92DA-42F5-8CB3-AFF22149E32C}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -17140,7 +17514,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -17148,7 +17522,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -17167,7 +17541,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -17280,7 +17654,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10" s="8">
         <v>0.90059708438022501</v>
@@ -17297,7 +17671,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -17313,7 +17687,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -17332,7 +17706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD06982F-F213-46C9-B847-8A938A2B8BE6}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -17353,7 +17727,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -17361,7 +17735,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -17380,7 +17754,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -17487,7 +17861,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -17498,7 +17872,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -17514,208 +17888,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="31"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B18"/>
-  </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DEF235-C456-41FF-80A3-33629F74B6A9}">
-  <sheetPr>
-    <tabColor theme="2" tint="-0.499984740745262"/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="13">
-        <v>24</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.60113635242414298</v>
-      </c>
-      <c r="E4" s="1">
-        <v>7.32088247502523E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="16">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.64963341878777003</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4.1779938274137902E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="16">
-        <v>37.9</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.70043986926395096</v>
-      </c>
-      <c r="E6" s="1">
-        <v>7.1396099744726604E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="16">
-        <v>21.9</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.80051318080794298</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.10902166337402799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="17">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.90135628705611903</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.12895203618756801</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="30"/>
-    </row>
-    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
         <v>150</v>
-      </c>
-      <c r="B13" s="31"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="30"/>
-    </row>
-    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
-        <v>151</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -17973,6 +18146,207 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DEF235-C456-41FF-80A3-33629F74B6A9}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
+    <col min="5" max="12" width="11.33203125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="13">
+        <v>24</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.60113635242414298</v>
+      </c>
+      <c r="E4" s="1">
+        <v>7.32088247502523E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="16">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.64963341878777003</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4.1779938274137902E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
+        <v>37.9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.70043986926395096</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.1396099744726604E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="16">
+        <v>21.9</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.80051318080794298</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.10902166337402799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="17">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.90135628705611903</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.12895203618756801</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="30"/>
+    </row>
+    <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="30"/>
+    </row>
+    <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="31"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD9B890-4B9E-49FD-9A3A-4A093331C053}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -17993,7 +18367,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -18001,7 +18375,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -18020,7 +18394,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -18133,7 +18507,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -18144,7 +18518,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -18160,7 +18534,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -18179,7 +18553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9E960F-E4A3-4E03-932A-87B59EED5DF6}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -18200,7 +18574,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -18208,7 +18582,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -18227,7 +18601,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -18328,7 +18702,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -18339,7 +18713,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -18355,7 +18729,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -18374,7 +18748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D473D8-8438-46EA-8367-88736D1A8666}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -18395,7 +18769,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -18403,7 +18777,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -18422,7 +18796,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -18535,7 +18909,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D10" s="8">
         <v>0.90073855243722301</v>
@@ -18552,7 +18926,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -18568,7 +18942,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -18587,7 +18961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387104F1-B47D-4336-A36C-1FF44F8E85EA}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -18608,7 +18982,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -18616,7 +18990,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -18635,7 +19009,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -18748,7 +19122,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -18759,7 +19133,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -18775,7 +19149,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
@@ -18794,7 +19168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D3A03CE-8CC8-4E1B-8010-5D77D5D732C7}">
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
@@ -18815,7 +19189,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -18823,7 +19197,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>4</v>
@@ -18842,7 +19216,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>7</v>
@@ -18943,7 +19317,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -18954,7 +19328,7 @@
     </row>
     <row r="13" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="31"/>
     </row>
@@ -18970,7 +19344,7 @@
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="31"/>
     </row>
